--- a/data-science/reports/model_reports/model_comparison.xlsx
+++ b/data-science/reports/model_reports/model_comparison.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -497,7 +497,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.2516</v>
+        <v>0.3794</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -541,7 +541,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.1373</v>
+        <v>0.2049</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -550,17 +550,17 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>{"alpha": 0.9, "ccp_alpha": 0.0, "criterion": "deprecated", "init": null, "learning_rate": 0.05, "loss": "squared_error", "max_depth": 3, "max_features": null, "max_leaf_nodes": null, "min_impurity_decrease": 0.0, "min_samples_leaf": 1, "min_samples_split": 2, "min_weight_fraction_leaf": 0.0, "n_estimators": 150, "n_iter_no_change": null, "random_state": 42, "subsample": 1.0, "tol": 0.0001, "validation_fraction": 0.1, "verbose": 0, "warm_start": false}</t>
+          <t>{"alpha": 0.9, "ccp_alpha": 0.0, "criterion": "friedman_mse", "init": null, "learning_rate": 0.05, "loss": "squared_error", "max_depth": 3, "max_features": null, "max_leaf_nodes": null, "min_impurity_decrease": 0.0, "min_samples_leaf": 1, "min_samples_split": 2, "min_weight_fraction_leaf": 0.0, "n_estimators": 150, "n_iter_no_change": null, "random_state": 42, "subsample": 1.0, "tol": 0.0001, "validation_fraction": 0.1, "verbose": 0, "warm_start": false}</t>
         </is>
       </c>
       <c r="E3" t="n">
         <v>0.2932</v>
       </c>
       <c r="F3" t="n">
-        <v>0.3582</v>
+        <v>0.3581</v>
       </c>
       <c r="G3" t="n">
-        <v>-0.3588</v>
+        <v>-0.3585</v>
       </c>
       <c r="H3" t="n">
         <v>0.1542</v>
@@ -585,7 +585,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.0037</v>
+        <v>0.0042</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -629,7 +629,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.0152</v>
+        <v>0.0163</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
